--- a/data/trans_dic/P2A_ner_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,2</t>
+          <t>0,79; 3,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,94</t>
+          <t>2,01; 5,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 5,17</t>
+          <t>1,65; 5,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,66</t>
+          <t>2,11; 5,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,49</t>
+          <t>0,61; 3,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 5,42</t>
+          <t>1,24; 5,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,96; 9,66</t>
+          <t>3,91; 9,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,39</t>
+          <t>1,3; 3,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,83</t>
+          <t>0,94; 2,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,91</t>
+          <t>1,94; 4,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 6,1</t>
+          <t>3,09; 6,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,23</t>
+          <t>1,98; 4,11</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,57</t>
+          <t>1,8; 5,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 6,84</t>
+          <t>2,42; 6,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,66</t>
+          <t>1,9; 5,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,34</t>
+          <t>1,27; 4,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,76</t>
+          <t>1,84; 5,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 7,64</t>
+          <t>2,55; 7,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 7,24</t>
+          <t>2,57; 7,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,87</t>
+          <t>2,95; 6,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,83</t>
+          <t>2,25; 4,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,92; 6,17</t>
+          <t>2,93; 6,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,69</t>
+          <t>2,69; 5,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,84</t>
+          <t>2,37; 4,7</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,7</t>
+          <t>1,81; 4,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,75</t>
+          <t>2,19; 5,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 8,11</t>
+          <t>3,84; 7,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,22</t>
+          <t>0,65; 4,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 10,97</t>
+          <t>2,49; 10,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 7,32</t>
+          <t>1,98; 7,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,59; 21,02</t>
+          <t>9,43; 21,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,48</t>
+          <t>2,7; 7,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,1</t>
+          <t>2,28; 5,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,7</t>
+          <t>2,35; 4,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 9,9</t>
+          <t>5,97; 10,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,5</t>
+          <t>1,03; 4,42</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,3</t>
+          <t>2,26; 4,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,37</t>
+          <t>1,49; 3,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,02</t>
+          <t>3,54; 6,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,31</t>
+          <t>2,19; 4,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,26</t>
+          <t>3,02; 6,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,79</t>
+          <t>3,33; 6,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 11,35</t>
+          <t>7,17; 11,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 59,75</t>
+          <t>3,69; 54,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,54</t>
+          <t>2,82; 4,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,29</t>
+          <t>2,48; 4,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,49; 7,65</t>
+          <t>5,46; 7,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 38,42</t>
+          <t>3,34; 42,02</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,48</t>
+          <t>1,6; 5,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,46</t>
+          <t>2,11; 5,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,33</t>
+          <t>3,7; 7,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 7,2</t>
+          <t>3,08; 7,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,51; 7,34</t>
+          <t>3,67; 7,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 8,19</t>
+          <t>4,76; 8,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,93; 19,55</t>
+          <t>13,64; 19,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,79; 6,8</t>
+          <t>3,82; 6,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 5,85</t>
+          <t>3,21; 6,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,03; 6,72</t>
+          <t>4,04; 6,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,63; 13,25</t>
+          <t>9,7; 13,41</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 6,25</t>
+          <t>3,96; 6,38</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,52</t>
+          <t>0,63; 3,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,94</t>
+          <t>0,69; 3,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,9</t>
+          <t>1,71; 6,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,72</t>
+          <t>0,36; 5,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,16; 6,7</t>
+          <t>4,1; 6,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,86; 6,57</t>
+          <t>3,78; 6,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,17; 14,41</t>
+          <t>10,32; 14,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,12; 6,85</t>
+          <t>4,04; 6,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,73; 5,97</t>
+          <t>3,7; 5,83</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,24; 5,64</t>
+          <t>3,34; 5,45</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,89; 12,35</t>
+          <t>8,84; 12,34</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,01</t>
+          <t>3,46; 6,0</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,39</t>
+          <t>2,25; 3,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,61</t>
+          <t>2,45; 3,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,87; 5,31</t>
+          <t>3,89; 5,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,74</t>
+          <t>2,29; 3,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,89; 5,29</t>
+          <t>3,9; 5,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,17; 5,67</t>
+          <t>4,18; 5,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,93; 12,12</t>
+          <t>9,92; 12,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,26; 26,92</t>
+          <t>4,28; 27,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,28; 4,21</t>
+          <t>3,26; 4,18</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,52; 4,47</t>
+          <t>3,53; 4,48</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,19; 8,53</t>
+          <t>7,28; 8,54</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,61; 15,77</t>
+          <t>3,6; 16,45</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3921; 15179</t>
+          <t>3720; 14573</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8767; 25963</t>
+          <t>8790; 25249</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6609; 22175</t>
+          <t>7088; 22436</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10919; 28615</t>
+          <t>10655; 27775</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1872; 10700</t>
+          <t>1866; 10812</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3999; 17039</t>
+          <t>3914; 16530</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13745; 33516</t>
+          <t>13576; 32830</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5497; 15180</t>
+          <t>5819; 15559</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7433; 22098</t>
+          <t>7349; 21064</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14795; 36927</t>
+          <t>14566; 34856</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22965; 47346</t>
+          <t>23978; 48070</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19569; 40314</t>
+          <t>18842; 39186</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6246; 20436</t>
+          <t>6593; 20838</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10280; 28638</t>
+          <t>10147; 28921</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7215; 21348</t>
+          <t>7176; 22410</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5056; 19605</t>
+          <t>5753; 20957</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7102; 21437</t>
+          <t>6827; 21308</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8877; 25829</t>
+          <t>8612; 24953</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9779; 26970</t>
+          <t>9564; 27069</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10772; 26279</t>
+          <t>11272; 26144</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16140; 35709</t>
+          <t>16597; 36569</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22119; 46692</t>
+          <t>22208; 46247</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20803; 42666</t>
+          <t>20160; 41365</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19614; 40399</t>
+          <t>19783; 39262</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9037; 25512</t>
+          <t>9828; 25170</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13123; 29874</t>
+          <t>13815; 32908</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20466; 42331</t>
+          <t>20063; 41200</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4621; 28192</t>
+          <t>4357; 29715</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4180; 18400</t>
+          <t>4179; 17722</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5199; 19045</t>
+          <t>5153; 18846</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15939; 34916</t>
+          <t>15669; 35191</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4483; 12485</t>
+          <t>4499; 12691</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16779; 36189</t>
+          <t>16223; 36382</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21274; 41815</t>
+          <t>20911; 43292</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39647; 68150</t>
+          <t>41056; 71051</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9457; 37607</t>
+          <t>8568; 36881</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27557; 53221</t>
+          <t>27951; 52313</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17802; 39032</t>
+          <t>17274; 38982</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39609; 69160</t>
+          <t>40736; 69579</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22938; 44621</t>
+          <t>22651; 43579</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21751; 44721</t>
+          <t>21537; 45224</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26222; 52022</t>
+          <t>25533; 48842</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59854; 93764</t>
+          <t>59205; 93590</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35358; 584428</t>
+          <t>36122; 528542</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53809; 88660</t>
+          <t>55030; 88708</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48042; 82638</t>
+          <t>47819; 81307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>108382; 151068</t>
+          <t>107837; 151960</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>65870; 773350</t>
+          <t>67146; 845847</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5884; 19218</t>
+          <t>5604; 19290</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9767; 27863</t>
+          <t>10758; 27895</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23585; 45472</t>
+          <t>22949; 44683</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15364; 34185</t>
+          <t>14618; 33888</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19939; 41771</t>
+          <t>20854; 42052</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35046; 62390</t>
+          <t>36284; 64135</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>102816; 144292</t>
+          <t>100682; 141191</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>31862; 57215</t>
+          <t>32118; 58551</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29201; 53804</t>
+          <t>29532; 56082</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>51309; 85427</t>
+          <t>51351; 84046</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>130849; 180007</t>
+          <t>131787; 182269</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>52021; 82262</t>
+          <t>52104; 84021</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1896; 10498</t>
+          <t>1868; 10136</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1844; 10510</t>
+          <t>1853; 10544</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4873; 16930</t>
+          <t>4910; 17830</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>878; 13752</t>
+          <t>862; 12622</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>51989; 83675</t>
+          <t>51197; 83077</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42803; 72853</t>
+          <t>41982; 71522</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>110032; 155947</t>
+          <t>111653; 155671</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>31339; 52133</t>
+          <t>30776; 53163</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>57657; 92405</t>
+          <t>57293; 90234</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44524; 77634</t>
+          <t>45927; 75003</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>121715; 169101</t>
+          <t>121066; 168902</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>35152; 60170</t>
+          <t>34662; 60101</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>73327; 110840</t>
+          <t>73512; 110054</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>83081; 123433</t>
+          <t>83815; 124211</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>131101; 179647</t>
+          <t>131565; 178462</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>74365; 126262</t>
+          <t>77453; 124947</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>131451; 178691</t>
+          <t>131728; 180654</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>147891; 201311</t>
+          <t>148511; 202093</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>350571; 427854</t>
+          <t>350254; 430591</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>152346; 963300</t>
+          <t>153023; 977834</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>218364; 279809</t>
+          <t>216517; 277614</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>245531; 311322</t>
+          <t>246407; 312330</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>497514; 590193</t>
+          <t>503363; 591015</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>251185; 1096573</t>
+          <t>250022; 1143922</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_ner_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,08</t>
+          <t>0,81; 3,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,77</t>
+          <t>2,0; 6,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,23</t>
+          <t>1,62; 5,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,5</t>
+          <t>2,15; 5,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,53</t>
+          <t>0,6; 3,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,26</t>
+          <t>1,17; 5,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,91; 9,46</t>
+          <t>3,82; 9,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,48</t>
+          <t>1,36; 3,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,7</t>
+          <t>0,94; 2,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,64</t>
+          <t>2,06; 4,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 6,19</t>
+          <t>2,97; 6,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,11</t>
+          <t>2,1; 4,2</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,68</t>
+          <t>1,87; 5,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,91</t>
+          <t>2,45; 6,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,94</t>
+          <t>2,06; 5,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,63</t>
+          <t>1,22; 4,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,73</t>
+          <t>1,89; 5,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 7,38</t>
+          <t>2,54; 7,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 7,27</t>
+          <t>2,21; 6,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 6,83</t>
+          <t>2,88; 6,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,95</t>
+          <t>2,24; 4,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,11</t>
+          <t>2,8; 6,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 5,52</t>
+          <t>2,58; 5,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,7</t>
+          <t>2,44; 4,93</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,64</t>
+          <t>1,71; 4,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,23</t>
+          <t>2,09; 4,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,89</t>
+          <t>3,85; 8,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,45</t>
+          <t>2,42; 6,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 10,56</t>
+          <t>2,46; 10,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 7,24</t>
+          <t>1,92; 6,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,43; 21,18</t>
+          <t>9,07; 21,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 7,6</t>
+          <t>2,91; 8,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,12</t>
+          <t>2,36; 5,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,87</t>
+          <t>2,36; 4,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,97; 10,33</t>
+          <t>5,8; 9,98</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,42</t>
+          <t>3,08; 6,16</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,22</t>
+          <t>2,17; 4,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,36</t>
+          <t>1,53; 3,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 6,05</t>
+          <t>3,55; 6,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,21</t>
+          <t>2,12; 4,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,02; 6,33</t>
+          <t>3,01; 5,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,37</t>
+          <t>3,28; 6,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,17; 11,33</t>
+          <t>7,21; 11,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,69; 54,04</t>
+          <t>3,31; 5,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 4,54</t>
+          <t>2,79; 4,64</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,22</t>
+          <t>2,54; 4,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 7,69</t>
+          <t>5,43; 7,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 42,02</t>
+          <t>2,85; 4,4</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,5</t>
+          <t>1,69; 5,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,46</t>
+          <t>2,13; 5,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,2</t>
+          <t>3,86; 7,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,08; 7,13</t>
+          <t>2,77; 6,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,39</t>
+          <t>3,54; 7,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,76; 8,42</t>
+          <t>4,76; 8,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,64; 19,13</t>
+          <t>13,8; 19,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,96</t>
+          <t>4,89; 7,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,1</t>
+          <t>3,17; 6,13</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 6,61</t>
+          <t>4,04; 6,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,7; 13,41</t>
+          <t>9,75; 13,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,96; 6,38</t>
+          <t>4,22; 6,48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,4</t>
+          <t>0,61; 3,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,95</t>
+          <t>0,7; 3,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,21</t>
+          <t>1,8; 6,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 5,25</t>
+          <t>0,35; 4,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,1; 6,65</t>
+          <t>4,19; 6,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,78; 6,45</t>
+          <t>3,75; 6,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,32; 14,39</t>
+          <t>10,35; 14,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,04; 6,98</t>
+          <t>3,88; 6,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,7; 5,83</t>
+          <t>3,63; 5,89</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,45</t>
+          <t>3,4; 5,64</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,84; 12,34</t>
+          <t>8,82; 12,24</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,46; 6,0</t>
+          <t>3,23; 5,53</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,37</t>
+          <t>2,27; 3,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,63</t>
+          <t>2,46; 3,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,89; 5,27</t>
+          <t>3,84; 5,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 3,7</t>
+          <t>2,72; 3,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,9; 5,35</t>
+          <t>3,97; 5,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,18; 5,69</t>
+          <t>4,24; 5,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,92; 12,19</t>
+          <t>9,96; 12,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,28; 27,33</t>
+          <t>4,13; 5,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,26; 4,18</t>
+          <t>3,24; 4,16</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,53; 4,48</t>
+          <t>3,52; 4,46</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,28; 8,54</t>
+          <t>7,16; 8,54</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,6; 16,45</t>
+          <t>3,58; 4,47</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17949</t>
+          <t>19881</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27545</t>
+          <t>30610</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3720; 14573</t>
+          <t>3831; 14574</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8790; 25249</t>
+          <t>8735; 27454</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7088; 22436</t>
+          <t>6940; 22181</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10655; 27775</t>
+          <t>11840; 30630</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1866; 10812</t>
+          <t>1844; 10921</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3914; 16530</t>
+          <t>3672; 16258</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13576; 32830</t>
+          <t>13242; 32185</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5819; 15559</t>
+          <t>6619; 17648</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7349; 21064</t>
+          <t>7328; 21575</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14566; 34856</t>
+          <t>15489; 36879</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23978; 48070</t>
+          <t>23054; 47620</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18842; 39186</t>
+          <t>21825; 43637</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11064</t>
+          <t>11924</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17259</t>
+          <t>19045</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28323</t>
+          <t>30969</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6593; 20838</t>
+          <t>6869; 21266</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10147; 28921</t>
+          <t>10247; 27941</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7176; 22410</t>
+          <t>7764; 22438</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5753; 20957</t>
+          <t>5872; 23352</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6827; 21308</t>
+          <t>7016; 20554</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8612; 24953</t>
+          <t>8601; 25221</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9564; 27069</t>
+          <t>8228; 24763</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11272; 26144</t>
+          <t>12195; 28134</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16597; 36569</t>
+          <t>16562; 36166</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22208; 46247</t>
+          <t>21207; 45788</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20160; 41365</t>
+          <t>19332; 42705</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19783; 39262</t>
+          <t>22093; 44697</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15619</t>
+          <t>19457</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7721</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23340</t>
+          <t>28835</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9828; 25170</t>
+          <t>9252; 25129</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13815; 32908</t>
+          <t>13132; 30209</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20063; 41200</t>
+          <t>20117; 42063</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4357; 29715</t>
+          <t>11423; 30271</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4179; 17722</t>
+          <t>4124; 18100</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5153; 18846</t>
+          <t>4991; 17471</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15669; 35191</t>
+          <t>15061; 35707</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4499; 12691</t>
+          <t>5465; 16149</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16223; 36382</t>
+          <t>16736; 37255</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20911; 43292</t>
+          <t>21031; 42454</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41056; 71051</t>
+          <t>39936; 68660</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8568; 36881</t>
+          <t>20329; 40581</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32045</t>
+          <t>34242</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>236496</t>
+          <t>37221</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>268541</t>
+          <t>71463</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27951; 52313</t>
+          <t>26866; 53248</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17274; 38982</t>
+          <t>17708; 40280</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40736; 69579</t>
+          <t>40791; 71488</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22651; 43579</t>
+          <t>24005; 46638</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21537; 45224</t>
+          <t>21503; 42066</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25533; 48842</t>
+          <t>25134; 49072</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59205; 93590</t>
+          <t>59556; 91950</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36122; 528542</t>
+          <t>28467; 47674</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>55030; 88708</t>
+          <t>54553; 90614</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>47819; 81307</t>
+          <t>48968; 81562</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>107837; 151960</t>
+          <t>107241; 152395</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>67146; 845847</t>
+          <t>56876; 87755</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23185</t>
+          <t>24351</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>44692</t>
+          <t>50937</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>67877</t>
+          <t>75288</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5604; 19290</t>
+          <t>5925; 20080</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10758; 27895</t>
+          <t>10892; 27375</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22949; 44683</t>
+          <t>23970; 45991</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14618; 33888</t>
+          <t>15714; 35467</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>20854; 42052</t>
+          <t>20145; 42862</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36284; 64135</t>
+          <t>36275; 62146</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>100682; 141191</t>
+          <t>101856; 141212</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>32118; 58551</t>
+          <t>40624; 62887</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29532; 56082</t>
+          <t>29164; 56352</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>51351; 84046</t>
+          <t>51379; 84312</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131787; 182269</t>
+          <t>132483; 177560</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>52104; 84021</t>
+          <t>59080; 90696</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>3426</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>40815</t>
+          <t>43496</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>44975</t>
+          <t>46921</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1868; 10136</t>
+          <t>1818; 11472</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1853; 10544</t>
+          <t>1858; 10423</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4910; 17830</t>
+          <t>5161; 18125</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>862; 12622</t>
+          <t>831; 10753</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>51197; 83077</t>
+          <t>52299; 83513</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>41982; 71522</t>
+          <t>41555; 72174</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>111653; 155671</t>
+          <t>111980; 154700</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>30776; 53163</t>
+          <t>32785; 56085</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>57293; 90234</t>
+          <t>56163; 91155</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>45927; 75003</t>
+          <t>46847; 77679</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>121066; 168902</t>
+          <t>120751; 167636</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>34662; 60101</t>
+          <t>34943; 59831</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>104022</t>
+          <t>113281</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>356581</t>
+          <t>170806</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>460602</t>
+          <t>284086</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>73512; 110054</t>
+          <t>74296; 111671</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>83815; 124211</t>
+          <t>84116; 125128</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>131565; 178462</t>
+          <t>130015; 179602</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>77453; 124947</t>
+          <t>93733; 136962</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>131728; 180654</t>
+          <t>134048; 182198</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>148511; 202093</t>
+          <t>150629; 202903</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>350254; 430591</t>
+          <t>351601; 428009</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>153023; 977834</t>
+          <t>150156; 197664</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>216517; 277614</t>
+          <t>215436; 276628</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>246407; 312330</t>
+          <t>245424; 311181</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>503363; 591015</t>
+          <t>495034; 590774</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>250022; 1143922</t>
+          <t>253127; 316646</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_ner_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
